--- a/猫饭NRC配方计算器.xlsx
+++ b/猫饭NRC配方计算器.xlsx
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基于 NRC 2006 · 鲅鱼体系 · 每批额外补1粒VD3</t>
+          <t>基于 NRC 2006 · 鲅鱼体系 · 建议每批补1粒VD3(不补也达标)</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="B57" s="13">
-        <f>D8/100*50+D9/100*7+D10/100*31+D12/100*520+D13/100*11078+D14/100*16898+D15/100*98+D16/100*150+D17/100*24</f>
+        <f>D8/100*50+D9/100*7+D10/100*31+D12/100*520+D13/100*11078+D14/100*16898+D15/100*98+D16/100*150+D17/100*80</f>
         <v/>
       </c>
       <c r="C57" s="13" t="n">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="B58" s="13">
-        <f>D8/100*5+D9/100*12+D12/100*82+D13/100*12+D14/100*49+D15/100*16</f>
+        <f>D9/100*12+D12/100*82+D13/100*8+D14/100*49+D15/100*292+D16/100*24+D17/100*4</f>
         <v/>
       </c>
       <c r="C58" s="13">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="B66" s="13">
-        <f>D8/100*6+D9/100*1+D10/100*72+D11/100*3+D12/100*47+D13/100*588+D14/100*290+D15/100*2+D16/100*1+D17/100*5</f>
+        <f>D8/100*6+D9/100*1+D10/100*72+D11/100*3+D12/100*47+D13/100*588+D14/100*290+D15/100*2+D16/100*1+D17/100*25</f>
         <v/>
       </c>
       <c r="C66" s="13">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="B67" s="13">
-        <f>D8/100*1.01+D9/100*0.6+D10/100*2.51+D11/100*2.25+D12/100*1.53+D13/100*6.5+D14/100*7.17+D15/100*0.42+D16/100*0.53+D17/100*1.03</f>
+        <f>D8/100*1.01+D9/100*0.6+D10/100*2.51+D11/100*2.25+D12/100*1.53+D13/100*6.5+D14/100*7.17+D15/100*0.42+D16/100*0.53+D17/100*1.6</f>
         <v/>
       </c>
       <c r="C67" s="13">
@@ -2216,7 +2216,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基于 NRC 2006 · 鲅鱼体系 · 每批额外补1粒VD3</t>
+          <t>基于 NRC 2006 · 鲅鱼体系 · 建议每批补1粒VD3(不补也达标)</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="B57" s="13">
-        <f>D8/100*50+D9/100*7+D10/100*31+D12/100*520+D13/100*11078+D14/100*16898+D15/100*98+D16/100*150+D17/100*24</f>
+        <f>D8/100*50+D9/100*7+D10/100*31+D12/100*520+D13/100*11078+D14/100*16898+D15/100*98+D16/100*150+D17/100*80</f>
         <v/>
       </c>
       <c r="C57" s="13" t="n">
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="B58" s="13">
-        <f>D8/100*5+D9/100*12+D12/100*82+D13/100*12+D14/100*49+D15/100*16</f>
+        <f>D9/100*12+D12/100*82+D13/100*8+D14/100*49+D15/100*292+D16/100*24+D17/100*4</f>
         <v/>
       </c>
       <c r="C58" s="13">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="B66" s="13">
-        <f>D8/100*6+D9/100*1+D10/100*72+D11/100*3+D12/100*47+D13/100*588+D14/100*290+D15/100*2+D16/100*1+D17/100*5</f>
+        <f>D8/100*6+D9/100*1+D10/100*72+D11/100*3+D12/100*47+D13/100*588+D14/100*290+D15/100*2+D16/100*1+D17/100*25</f>
         <v/>
       </c>
       <c r="C66" s="13">
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="B67" s="13">
-        <f>D8/100*1.01+D9/100*0.6+D10/100*2.51+D11/100*2.25+D12/100*1.53+D13/100*6.5+D14/100*7.17+D15/100*0.42+D16/100*0.53+D17/100*1.03</f>
+        <f>D8/100*1.01+D9/100*0.6+D10/100*2.51+D11/100*2.25+D12/100*1.53+D13/100*6.5+D14/100*7.17+D15/100*0.42+D16/100*0.53+D17/100*1.6</f>
         <v/>
       </c>
       <c r="C67" s="13">
@@ -3883,7 +3883,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基于 NRC 2006 · 鲅鱼体系 · 每批额外补1粒VD3</t>
+          <t>基于 NRC 2006 · 鲅鱼体系 · 建议每批补1粒VD3(不补也达标)</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="B57" s="13">
-        <f>D8/100*50+D9/100*7+D10/100*31+D12/100*520+D13/100*11078+D14/100*16898+D15/100*98+D16/100*150+D17/100*24</f>
+        <f>D8/100*50+D9/100*7+D10/100*31+D12/100*520+D13/100*11078+D14/100*16898+D15/100*98+D16/100*150+D17/100*80</f>
         <v/>
       </c>
       <c r="C57" s="13" t="n">
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="B58" s="13">
-        <f>D8/100*5+D9/100*12+D12/100*82+D13/100*12+D14/100*49+D15/100*16</f>
+        <f>D9/100*12+D12/100*82+D13/100*8+D14/100*49+D15/100*292+D16/100*24+D17/100*4</f>
         <v/>
       </c>
       <c r="C58" s="13">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="B66" s="13">
-        <f>D8/100*6+D9/100*1+D10/100*72+D11/100*3+D12/100*47+D13/100*588+D14/100*290+D15/100*2+D16/100*1+D17/100*5</f>
+        <f>D8/100*6+D9/100*1+D10/100*72+D11/100*3+D12/100*47+D13/100*588+D14/100*290+D15/100*2+D16/100*1+D17/100*25</f>
         <v/>
       </c>
       <c r="C66" s="13">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="B67" s="13">
-        <f>D8/100*1.01+D9/100*0.6+D10/100*2.51+D11/100*2.25+D12/100*1.53+D13/100*6.5+D14/100*7.17+D15/100*0.42+D16/100*0.53+D17/100*1.03</f>
+        <f>D8/100*1.01+D9/100*0.6+D10/100*2.51+D11/100*2.25+D12/100*1.53+D13/100*6.5+D14/100*7.17+D15/100*0.42+D16/100*0.53+D17/100*1.6</f>
         <v/>
       </c>
       <c r="C67" s="13">
@@ -6123,7 +6123,7 @@
         <v>150</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="B18" s="19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C18" s="19" t="n">
         <v>12</v>
@@ -6148,19 +6148,19 @@
         <v>82</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H18" s="19" t="n">
         <v>49</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>16</v>
+        <v>292</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K18" s="19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -6641,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -6678,7 +6678,7 @@
         <v>0.53</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/猫饭NRC配方计算器.xlsx
+++ b/猫饭NRC配方计算器.xlsx
@@ -904,16 +904,16 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>维生素E 100IU×8</t>
+          <t>维生素E 100IU×2</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>8粒</t>
+          <t>2粒</t>
         </is>
       </c>
       <c r="C31" s="15">
-        <f>ROUND(8.0*B5/3168,1)</f>
+        <f>ROUND(2.0*B5/3168,1)</f>
         <v/>
       </c>
     </row>
@@ -925,11 +925,11 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>2片</t>
+          <t>0.5片</t>
         </is>
       </c>
       <c r="C32" s="15">
-        <f>ROUND(2.0*B5/3168,1)</f>
+        <f>ROUND(0.5*B5/3168,1)</f>
         <v/>
       </c>
     </row>
@@ -973,11 +973,11 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>1粒</t>
+          <t>0.5粒</t>
         </is>
       </c>
       <c r="C35" s="15">
-        <f>ROUND(1.0*B5/3168,1)</f>
+        <f>ROUND(0.5*B5/3168,1)</f>
         <v/>
       </c>
     </row>
@@ -989,11 +989,11 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>1粒</t>
+          <t>0.5粒</t>
         </is>
       </c>
       <c r="C36" s="15">
-        <f>ROUND(1.0*B5/3168,1)</f>
+        <f>ROUND(0.5*B5/3168,1)</f>
         <v/>
       </c>
     </row>
@@ -1005,11 +1005,11 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>1粒</t>
+          <t>0.5粒</t>
         </is>
       </c>
       <c r="C37" s="15">
-        <f>ROUND(1.0*B5/3168,1)</f>
+        <f>ROUND(0.5*B5/3168,1)</f>
         <v/>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v/>
       </c>
       <c r="C50" s="13">
-        <f>ROUND(36*B5/3168,1)</f>
+        <f>ROUND(18.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D50" s="13">
@@ -1380,7 +1380,7 @@
         <v/>
       </c>
       <c r="C51" s="13">
-        <f>ROUND(30*B5/3168,1)</f>
+        <f>ROUND(15.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D51" s="13">
@@ -1449,7 +1449,7 @@
         <v/>
       </c>
       <c r="C53" s="13">
-        <f>ROUND(10*B5/3168,1)</f>
+        <f>ROUND(5.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D53" s="13">
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="C59" s="13">
-        <f>ROUND(536.88*B5/3168,1)</f>
+        <f>ROUND(134.22*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D59" s="13">
@@ -1686,7 +1686,7 @@
         <v/>
       </c>
       <c r="C60" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D60" s="13">
@@ -1721,7 +1721,7 @@
         <v/>
       </c>
       <c r="C61" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D61" s="13">
@@ -1756,7 +1756,7 @@
         <v/>
       </c>
       <c r="C62" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D62" s="13">
@@ -1791,7 +1791,7 @@
         <v/>
       </c>
       <c r="C63" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D63" s="13">
@@ -1826,7 +1826,7 @@
         <v/>
       </c>
       <c r="C64" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D64" s="13">
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="C66" s="13">
-        <f>ROUND(800*B5/3168,1)</f>
+        <f>ROUND(200.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D66" s="13">
@@ -1930,7 +1930,7 @@
         <v/>
       </c>
       <c r="C67" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D67" s="13">
@@ -2571,16 +2571,16 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>维生素E 100IU×8</t>
+          <t>维生素E 100IU×2</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>8粒</t>
+          <t>2粒</t>
         </is>
       </c>
       <c r="C31" s="15">
-        <f>ROUND(8.0*B5/3168,1)</f>
+        <f>ROUND(2.0*B5/3168,1)</f>
         <v/>
       </c>
     </row>
@@ -2592,11 +2592,11 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>2片</t>
+          <t>0.5片</t>
         </is>
       </c>
       <c r="C32" s="15">
-        <f>ROUND(2.0*B5/3168,1)</f>
+        <f>ROUND(0.5*B5/3168,1)</f>
         <v/>
       </c>
     </row>
@@ -2640,11 +2640,11 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>1粒</t>
+          <t>0.5粒</t>
         </is>
       </c>
       <c r="C35" s="15">
-        <f>ROUND(1.0*B5/3168,1)</f>
+        <f>ROUND(0.5*B5/3168,1)</f>
         <v/>
       </c>
     </row>
@@ -2656,11 +2656,11 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>1粒</t>
+          <t>0.5粒</t>
         </is>
       </c>
       <c r="C36" s="15">
-        <f>ROUND(1.0*B5/3168,1)</f>
+        <f>ROUND(0.5*B5/3168,1)</f>
         <v/>
       </c>
     </row>
@@ -2672,11 +2672,11 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>1粒</t>
+          <t>0.5粒</t>
         </is>
       </c>
       <c r="C37" s="15">
-        <f>ROUND(1.0*B5/3168,1)</f>
+        <f>ROUND(0.5*B5/3168,1)</f>
         <v/>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
         <v/>
       </c>
       <c r="C50" s="13">
-        <f>ROUND(36*B5/3168,1)</f>
+        <f>ROUND(18.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D50" s="13">
@@ -3047,7 +3047,7 @@
         <v/>
       </c>
       <c r="C51" s="13">
-        <f>ROUND(30*B5/3168,1)</f>
+        <f>ROUND(15.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D51" s="13">
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
       <c r="C53" s="13">
-        <f>ROUND(10*B5/3168,1)</f>
+        <f>ROUND(5.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D53" s="13">
@@ -3318,7 +3318,7 @@
         <v/>
       </c>
       <c r="C59" s="13">
-        <f>ROUND(536.88*B5/3168,1)</f>
+        <f>ROUND(134.22*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D59" s="13">
@@ -3353,7 +3353,7 @@
         <v/>
       </c>
       <c r="C60" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D60" s="13">
@@ -3388,7 +3388,7 @@
         <v/>
       </c>
       <c r="C61" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D61" s="13">
@@ -3423,7 +3423,7 @@
         <v/>
       </c>
       <c r="C62" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D62" s="13">
@@ -3458,7 +3458,7 @@
         <v/>
       </c>
       <c r="C63" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D63" s="13">
@@ -3493,7 +3493,7 @@
         <v/>
       </c>
       <c r="C64" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D64" s="13">
@@ -3562,7 +3562,7 @@
         <v/>
       </c>
       <c r="C66" s="13">
-        <f>ROUND(800*B5/3168,1)</f>
+        <f>ROUND(200.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D66" s="13">
@@ -3597,7 +3597,7 @@
         <v/>
       </c>
       <c r="C67" s="13">
-        <f>ROUND(100*B5/3168,1)</f>
+        <f>ROUND(25.0*B5/3168,1)</f>
         <v/>
       </c>
       <c r="D67" s="13">
@@ -4238,16 +4238,16 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>维生素E 100IU×8</t>
+          <t>维生素E 100IU×2</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>8粒</t>
+          <t>2粒</t>
         </is>
       </c>
       <c r="C31" s="15">
-        <f>ROUND(8.0*B5/3180,1)</f>
+        <f>ROUND(2.0*B5/3180,1)</f>
         <v/>
       </c>
     </row>
@@ -4259,11 +4259,11 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>2片</t>
+          <t>0.5片</t>
         </is>
       </c>
       <c r="C32" s="15">
-        <f>ROUND(2.0*B5/3180,1)</f>
+        <f>ROUND(0.5*B5/3180,1)</f>
         <v/>
       </c>
     </row>
@@ -4307,11 +4307,11 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>1粒</t>
+          <t>0.5粒</t>
         </is>
       </c>
       <c r="C35" s="15">
-        <f>ROUND(1.0*B5/3180,1)</f>
+        <f>ROUND(0.5*B5/3180,1)</f>
         <v/>
       </c>
     </row>
@@ -4323,11 +4323,11 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>1粒</t>
+          <t>0.5粒</t>
         </is>
       </c>
       <c r="C36" s="15">
-        <f>ROUND(1.0*B5/3180,1)</f>
+        <f>ROUND(0.5*B5/3180,1)</f>
         <v/>
       </c>
     </row>
@@ -4339,11 +4339,11 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>1粒</t>
+          <t>0.5粒</t>
         </is>
       </c>
       <c r="C37" s="15">
-        <f>ROUND(1.0*B5/3180,1)</f>
+        <f>ROUND(0.5*B5/3180,1)</f>
         <v/>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v/>
       </c>
       <c r="C50" s="13">
-        <f>ROUND(36*B5/3180,1)</f>
+        <f>ROUND(18.0*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D50" s="13">
@@ -4714,7 +4714,7 @@
         <v/>
       </c>
       <c r="C51" s="13">
-        <f>ROUND(30*B5/3180,1)</f>
+        <f>ROUND(15.0*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D51" s="13">
@@ -4783,7 +4783,7 @@
         <v/>
       </c>
       <c r="C53" s="13">
-        <f>ROUND(10*B5/3180,1)</f>
+        <f>ROUND(5.0*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D53" s="13">
@@ -4985,7 +4985,7 @@
         <v/>
       </c>
       <c r="C59" s="13">
-        <f>ROUND(536.88*B5/3180,1)</f>
+        <f>ROUND(134.22*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D59" s="13">
@@ -5020,7 +5020,7 @@
         <v/>
       </c>
       <c r="C60" s="13">
-        <f>ROUND(100*B5/3180,1)</f>
+        <f>ROUND(25.0*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D60" s="13">
@@ -5055,7 +5055,7 @@
         <v/>
       </c>
       <c r="C61" s="13">
-        <f>ROUND(100*B5/3180,1)</f>
+        <f>ROUND(25.0*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D61" s="13">
@@ -5090,7 +5090,7 @@
         <v/>
       </c>
       <c r="C62" s="13">
-        <f>ROUND(100*B5/3180,1)</f>
+        <f>ROUND(25.0*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D62" s="13">
@@ -5125,7 +5125,7 @@
         <v/>
       </c>
       <c r="C63" s="13">
-        <f>ROUND(100*B5/3180,1)</f>
+        <f>ROUND(25.0*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D63" s="13">
@@ -5160,7 +5160,7 @@
         <v/>
       </c>
       <c r="C64" s="13">
-        <f>ROUND(100*B5/3180,1)</f>
+        <f>ROUND(25.0*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D64" s="13">
@@ -5229,7 +5229,7 @@
         <v/>
       </c>
       <c r="C66" s="13">
-        <f>ROUND(800*B5/3180,1)</f>
+        <f>ROUND(200.0*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D66" s="13">
@@ -5264,7 +5264,7 @@
         <v/>
       </c>
       <c r="C67" s="13">
-        <f>ROUND(100*B5/3180,1)</f>
+        <f>ROUND(25.0*B5/3180,1)</f>
         <v/>
       </c>
       <c r="D67" s="13">
